--- a/PROCESSED FILES/TOA - CORRECT ANSWERS.xlsx
+++ b/PROCESSED FILES/TOA - CORRECT ANSWERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivans\Desktop\Archi Reviewer\PROCESSED FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF4FACD-F90A-440B-88BC-7D387D838086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519C7F5D-C024-4B45-A429-63E279126710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,33 +378,6 @@
     <t>Architect of the Reliance Building in Chicago [A] Eero Saarine [B] Eliel Saarinen [C] Oscar Niemeyer [D] Daniel Burnham</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve">A style of fine and appied art current in the late 19th and 20th century, characterized by fluid, undulating motifs, often derived from </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>natural forms</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve"> (D.K. Ching p. 134) [A] Arts and Crafts [B] Art Noveau [C] Bauhaus [D] Les Ecoles Beaux Arts</t>
-    </r>
-  </si>
-  <si>
     <t>It is the italian version of Art Noveaum named after the firm of liberty and co. in London (D.K. Ching p. 134) [A] Jugendstil [B] Stile Liberty [C] Sezession [D] Modernismo</t>
   </si>
   <si>
@@ -417,61 +390,7 @@
     <t>A school of design establish in Welmar Germany in 1919. moved to Dessau in 1926 and closed in 1933 as a result of Nazi Hostility. It characterized by the synthesis of technology, craft and design aesthetics with an emphasis on functionalism. (D.K. Ching p. 135) [A] Art Noveau [B] Bauhaus [C] Art Deco [D] Arts and Crafts</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve">A style of </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>painting and sculpture</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve"> developed in the early 20th century. Characterized by an emphasis on formal structure, reduction of natural forms to their geometrical equivalents. (D.K. Ching p. 135) [A] Brutalism [B] Cubism [C] Modernism [D] Abstract Expressionism</t>
-    </r>
-  </si>
-  <si>
     <t>A movement in architecture and decorative arts that developed in 1970's in reaction to the principles and practices of modernism, especially the influence of International Style, encouraging the use of elements from historical vernacular styles and often playful illusion, decoration and complexity (D.K. Ching p. 135) [A] Post Modernism [B] International Style [C] Modernism [D] Abstract Expressionism</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve">A functional architecture devoild of regional characteristics, developed in 1920's and 1930's in Western EU and US and applied throughout the world. Characterized by </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>simple geometric forms, large untextured, often white surfaces, large areas of glass and general use of steel and reinforced concrete</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve"> (D.K. Ching p. 135 (D.K. Ching p. 135) [A] Post Modernism [B] International Style [C] Modernism [D] Abstract Expressionism</t>
-    </r>
   </si>
   <si>
     <t>A deliberate philosophical and practical enstrangement from the past in the arts and literature occuring in the coarse of the 20th century and taking form in any of various innovative movement and styles (D.K. Ching p. 135) [A] Post Modernism [B] International Style [C] Modernism [D] Abstract Expressionism</t>
@@ -1478,6 +1397,72 @@
         <rFont val="Century Gothic"/>
       </rPr>
       <t>Form does not necessarily follow function". [A] Robert Mailart [B] Alvar Aalto [C] Frederick Law Omsltead [D] Antonio Gaudi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A style of fine and appied art current in the late 19th and 20th century, characterized by fluid, undulating motifs, often derived from </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>natural forms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t xml:space="preserve"> (D.K. Ching p. 134) [A] Arts and Crafts [B] Art Noveau [C] Bauhaus [D] Les Ecoles Beaux Arts</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A style of </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>painting and sculpture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t xml:space="preserve"> developed in the early 20th century. Characterized by an emphasis on formal structure, reduction of natural forms to their geometrical equivalents. (D.K. Ching p. 135) [A] Brutalism [B] Cubism [C] Modernism [D] Abstract Expressionism</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A functional architecture devoild of regional characteristics, developed in 1920's and 1930's in Western EU and US and applied throughout the world. Characterized by </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>simple geometric forms, large untextured, often white surfaces, large areas of glass and general use of steel and reinforced concrete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t xml:space="preserve"> (D.K. Ching p. 135 (D.K. Ching p. 135) [A] Post Modernism [B] International Style [C] Modernism [D] Abstract Expressionism</t>
     </r>
   </si>
 </sst>
@@ -2656,7 +2641,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -5384,7 +5369,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>117</v>
+        <v>414</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>7</v>
@@ -5415,7 +5400,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>7</v>
@@ -5446,7 +5431,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>3</v>
@@ -5477,7 +5462,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>1</v>
@@ -5508,7 +5493,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>7</v>
@@ -5539,7 +5524,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>122</v>
+        <v>415</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>7</v>
@@ -5570,7 +5555,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>5</v>
@@ -5601,7 +5586,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>124</v>
+        <v>416</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>7</v>
@@ -5632,7 +5617,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>1</v>
@@ -5663,7 +5648,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>3</v>
@@ -5694,7 +5679,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>5</v>
@@ -5725,7 +5710,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>1</v>
@@ -5756,7 +5741,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>1</v>
@@ -5787,7 +5772,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>7</v>
@@ -5818,7 +5803,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>7</v>
@@ -5849,7 +5834,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>7</v>
@@ -5880,7 +5865,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>7</v>
@@ -5911,7 +5896,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>7</v>
@@ -5942,7 +5927,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>3</v>
@@ -5973,7 +5958,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>1</v>
@@ -6004,7 +5989,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>3</v>
@@ -6035,7 +6020,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>1</v>
@@ -6066,7 +6051,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>3</v>
@@ -6097,7 +6082,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>7</v>
@@ -6128,7 +6113,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>1</v>
@@ -6159,7 +6144,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>5</v>
@@ -6190,7 +6175,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>7</v>
@@ -6221,7 +6206,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>3</v>
@@ -6252,7 +6237,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>7</v>
@@ -6283,7 +6268,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>7</v>
@@ -6314,7 +6299,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>7</v>
@@ -6345,7 +6330,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>1</v>
@@ -6376,7 +6361,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>7</v>
@@ -6407,7 +6392,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>1</v>
@@ -6438,7 +6423,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>1</v>
@@ -6469,7 +6454,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>1</v>
@@ -6500,7 +6485,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>3</v>
@@ -6531,7 +6516,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>7</v>
@@ -6562,7 +6547,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>1</v>
@@ -6593,7 +6578,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>7</v>
@@ -6624,7 +6609,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>7</v>
@@ -6655,7 +6640,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>1</v>
@@ -6686,7 +6671,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>5</v>
@@ -6717,7 +6702,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>7</v>
@@ -6748,7 +6733,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>1</v>
@@ -6779,7 +6764,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>1</v>
@@ -6810,7 +6795,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>1</v>
@@ -6841,7 +6826,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>7</v>
@@ -6872,7 +6857,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>1</v>
@@ -6903,7 +6888,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>3</v>
@@ -6934,7 +6919,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>1</v>
@@ -6965,7 +6950,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>5</v>
@@ -6996,7 +6981,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>7</v>
@@ -7027,7 +7012,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>7</v>
@@ -7058,7 +7043,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>1</v>
@@ -7089,7 +7074,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>5</v>
@@ -7120,7 +7105,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>1</v>
@@ -7151,7 +7136,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>1</v>
@@ -7182,7 +7167,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>7</v>
@@ -7213,7 +7198,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>3</v>
@@ -7244,7 +7229,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>5</v>
@@ -7275,7 +7260,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>1</v>
@@ -7306,7 +7291,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>3</v>
@@ -7337,7 +7322,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>1</v>
@@ -7368,7 +7353,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>3</v>
@@ -7399,7 +7384,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>3</v>
@@ -7430,7 +7415,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>1</v>
@@ -7461,7 +7446,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>1</v>
@@ -7492,7 +7477,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>7</v>
@@ -7523,7 +7508,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>5</v>
@@ -7554,7 +7539,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>1</v>
@@ -7585,7 +7570,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>7</v>
@@ -7616,7 +7601,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>1</v>
@@ -7647,7 +7632,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>5</v>
@@ -7678,7 +7663,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>7</v>
@@ -7709,7 +7694,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>3</v>
@@ -7740,7 +7725,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>5</v>
@@ -7771,7 +7756,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>5</v>
@@ -7802,7 +7787,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>5</v>
@@ -7833,7 +7818,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>1</v>
@@ -7864,7 +7849,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>7</v>
@@ -7895,7 +7880,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>5</v>
@@ -7926,7 +7911,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>5</v>
@@ -7957,7 +7942,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>3</v>
@@ -7988,7 +7973,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>3</v>
@@ -8019,7 +8004,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>5</v>
@@ -8050,7 +8035,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>5</v>
@@ -8081,7 +8066,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>5</v>
@@ -8112,7 +8097,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>1</v>
@@ -8143,7 +8128,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>1</v>
@@ -8174,7 +8159,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>1</v>
@@ -8205,7 +8190,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>7</v>
@@ -8236,7 +8221,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>1</v>
@@ -8267,7 +8252,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>7</v>
@@ -8298,7 +8283,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>7</v>
@@ -8329,7 +8314,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>5</v>
@@ -8360,7 +8345,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>5</v>
@@ -8391,7 +8376,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>1</v>
@@ -8422,7 +8407,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>7</v>
@@ -8453,7 +8438,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>1</v>
@@ -8484,7 +8469,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>7</v>
@@ -8515,7 +8500,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>5</v>
@@ -8546,7 +8531,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>7</v>
@@ -8577,7 +8562,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>1</v>
@@ -8608,7 +8593,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C219" s="11" t="s">
         <v>3</v>
@@ -8639,7 +8624,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>3</v>
@@ -8670,7 +8655,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>1</v>
@@ -8701,7 +8686,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>7</v>
@@ -8732,7 +8717,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>1</v>
@@ -8763,7 +8748,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>1</v>
@@ -8794,7 +8779,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>5</v>
@@ -8825,7 +8810,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>1</v>
@@ -8856,7 +8841,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>3</v>
@@ -8887,7 +8872,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>3</v>
@@ -8918,7 +8903,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>5</v>
@@ -8949,7 +8934,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>7</v>
@@ -8980,7 +8965,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>3</v>
@@ -9011,7 +8996,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>1</v>
@@ -9042,7 +9027,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>3</v>
@@ -9073,7 +9058,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>5</v>
@@ -9104,7 +9089,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>5</v>
@@ -9135,7 +9120,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>1</v>
@@ -9166,7 +9151,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>7</v>
@@ -9197,7 +9182,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>3</v>
@@ -9228,7 +9213,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>5</v>
@@ -9259,7 +9244,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>7</v>
@@ -9290,7 +9275,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C241" s="8" t="s">
         <v>7</v>
@@ -9321,7 +9306,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C242" s="8" t="s">
         <v>5</v>
@@ -9352,7 +9337,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>7</v>
@@ -9383,7 +9368,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>1</v>
@@ -9414,7 +9399,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>1</v>
@@ -9445,7 +9430,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>3</v>
@@ -9476,7 +9461,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C247" s="8" t="s">
         <v>5</v>
@@ -9507,7 +9492,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C248" s="8" t="s">
         <v>5</v>
@@ -9538,7 +9523,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>7</v>
@@ -9569,7 +9554,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>3</v>
@@ -9600,7 +9585,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>5</v>
@@ -9631,7 +9616,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>1</v>
@@ -9662,7 +9647,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>3</v>
@@ -9693,7 +9678,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C254" s="8" t="s">
         <v>1</v>
@@ -9724,7 +9709,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C255" s="8" t="s">
         <v>1</v>
@@ -9755,7 +9740,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>5</v>
@@ -9786,7 +9771,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>3</v>
@@ -9817,7 +9802,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C258" s="8" t="s">
         <v>3</v>
@@ -9848,7 +9833,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>1</v>
@@ -9879,7 +9864,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>7</v>
@@ -9910,7 +9895,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C261" s="6" t="s">
         <v>7</v>
@@ -9941,7 +9926,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C262" s="6" t="s">
         <v>7</v>
@@ -9972,7 +9957,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C263" s="6" t="s">
         <v>7</v>
@@ -10003,7 +9988,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C264" s="6" t="s">
         <v>5</v>
@@ -10034,7 +10019,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>1</v>
@@ -10065,7 +10050,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>3</v>
@@ -10096,7 +10081,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>5</v>
@@ -10127,7 +10112,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>7</v>
@@ -10158,7 +10143,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>3</v>
@@ -10189,7 +10174,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>5</v>
@@ -10220,7 +10205,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>1</v>
@@ -10251,7 +10236,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>7</v>
@@ -10282,7 +10267,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>1</v>
@@ -10313,7 +10298,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>3</v>
@@ -10344,7 +10329,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>7</v>
@@ -10375,7 +10360,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>1</v>
@@ -10406,7 +10391,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>5</v>
@@ -10437,7 +10422,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>7</v>
@@ -10468,7 +10453,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>5</v>
@@ -10499,7 +10484,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>7</v>
@@ -10530,7 +10515,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>1</v>
@@ -10561,7 +10546,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>7</v>
@@ -10592,7 +10577,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>3</v>
@@ -10623,7 +10608,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>5</v>
@@ -10654,7 +10639,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>1</v>
@@ -10685,7 +10670,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>5</v>
@@ -10716,7 +10701,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>1</v>
@@ -10747,7 +10732,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>7</v>
@@ -10778,7 +10763,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>3</v>
@@ -10809,7 +10794,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>1</v>
@@ -10840,7 +10825,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>5</v>
@@ -10871,7 +10856,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>7</v>
@@ -10902,7 +10887,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>1</v>
@@ -10933,7 +10918,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>3</v>
@@ -10964,7 +10949,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>5</v>
@@ -10995,7 +10980,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>7</v>
@@ -11026,7 +11011,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>5</v>
@@ -11057,7 +11042,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>7</v>
@@ -11088,7 +11073,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>3</v>
@@ -11119,7 +11104,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>1</v>
@@ -11150,7 +11135,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>7</v>
@@ -11181,7 +11166,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>5</v>
@@ -11212,7 +11197,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>1</v>
@@ -11243,7 +11228,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>7</v>
@@ -11274,7 +11259,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>5</v>
@@ -11305,7 +11290,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>1</v>
@@ -11336,7 +11321,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>7</v>
@@ -11367,7 +11352,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>5</v>
@@ -11398,7 +11383,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>5</v>
@@ -11429,7 +11414,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>5</v>
@@ -11460,7 +11445,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>7</v>
@@ -11491,7 +11476,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>1</v>
@@ -11522,7 +11507,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>7</v>
@@ -11553,7 +11538,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>7</v>
@@ -11584,7 +11569,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>5</v>
@@ -11615,7 +11600,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>5</v>
@@ -11646,7 +11631,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>7</v>
@@ -11677,7 +11662,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>5</v>
@@ -11708,7 +11693,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>1</v>
@@ -11739,7 +11724,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>7</v>
@@ -11770,7 +11755,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>5</v>
@@ -11801,7 +11786,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>1</v>
@@ -11832,7 +11817,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>1</v>
@@ -11863,7 +11848,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>1</v>
@@ -11894,7 +11879,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>5</v>
@@ -11925,7 +11910,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>7</v>
@@ -11956,7 +11941,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>7</v>
@@ -11987,7 +11972,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>3</v>
@@ -12018,7 +12003,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>5</v>
@@ -12049,7 +12034,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>3</v>
@@ -12080,7 +12065,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>1</v>
@@ -12111,7 +12096,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>7</v>
@@ -12142,7 +12127,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>1</v>
@@ -12173,7 +12158,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>7</v>
@@ -12204,7 +12189,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>5</v>
@@ -12235,7 +12220,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>1</v>
@@ -12266,7 +12251,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>5</v>
@@ -12297,7 +12282,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>5</v>
@@ -12328,7 +12313,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>5</v>
@@ -12359,7 +12344,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>1</v>
@@ -12390,7 +12375,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>7</v>
@@ -12421,7 +12406,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>1</v>
@@ -12452,7 +12437,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>1</v>
@@ -12483,7 +12468,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>7</v>
@@ -12514,7 +12499,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>1</v>
@@ -12545,7 +12530,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>7</v>
@@ -12576,7 +12561,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>1</v>
@@ -12607,7 +12592,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>7</v>
@@ -12638,7 +12623,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>5</v>
@@ -12669,7 +12654,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>1</v>
@@ -12700,7 +12685,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>7</v>
@@ -12731,7 +12716,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>3</v>
@@ -12762,7 +12747,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>7</v>
@@ -12793,10 +12778,10 @@
         <v>354</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D354" s="3"/>
       <c r="E354" s="3"/>
@@ -12824,10 +12809,10 @@
         <v>355</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D355" s="3"/>
       <c r="E355" s="3"/>
@@ -12855,7 +12840,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>5</v>
@@ -12886,7 +12871,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>7</v>
@@ -12917,7 +12902,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>1</v>
@@ -12948,7 +12933,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>3</v>
@@ -12979,7 +12964,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>1</v>
@@ -13010,7 +12995,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>1</v>
@@ -13041,7 +13026,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>1</v>
@@ -13072,7 +13057,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>1</v>
@@ -13103,7 +13088,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>7</v>
@@ -13134,7 +13119,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C365" s="11" t="s">
         <v>3</v>
@@ -13165,7 +13150,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>1</v>
@@ -13196,7 +13181,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>7</v>
@@ -13227,7 +13212,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>1</v>
@@ -13258,7 +13243,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>5</v>
@@ -13289,7 +13274,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>7</v>
@@ -13320,7 +13305,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>5</v>
@@ -13351,7 +13336,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>7</v>
@@ -13382,7 +13367,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>5</v>
@@ -13413,7 +13398,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>3</v>
@@ -13444,7 +13429,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>7</v>
@@ -13475,7 +13460,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>5</v>
@@ -13506,7 +13491,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>5</v>
@@ -13537,7 +13522,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>1</v>
@@ -13568,7 +13553,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>5</v>
@@ -13599,7 +13584,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>1</v>
@@ -13630,7 +13615,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="12" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C381" s="12" t="s">
         <v>5</v>
@@ -13661,7 +13646,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>3</v>
@@ -13692,7 +13677,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>1</v>
@@ -13723,7 +13708,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>7</v>
@@ -13754,7 +13739,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>5</v>
@@ -13785,7 +13770,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>3</v>
@@ -13816,7 +13801,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>3</v>
@@ -13847,7 +13832,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>1</v>
@@ -13878,7 +13863,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>7</v>
@@ -13909,7 +13894,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>5</v>
@@ -13940,7 +13925,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>1</v>
@@ -13971,7 +13956,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>7</v>
@@ -14002,7 +13987,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>1</v>
@@ -14033,7 +14018,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>7</v>
@@ -14064,7 +14049,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>1</v>
@@ -14095,7 +14080,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>1</v>
@@ -14126,7 +14111,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>1</v>
@@ -14157,7 +14142,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>7</v>
@@ -14188,7 +14173,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>5</v>
@@ -14219,7 +14204,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>3</v>
@@ -14250,7 +14235,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>7</v>
@@ -14281,7 +14266,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>1</v>
@@ -14312,7 +14297,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>1</v>
@@ -14343,7 +14328,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>1</v>
@@ -14374,7 +14359,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>1</v>
@@ -14405,7 +14390,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>1</v>
@@ -14436,7 +14421,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>1</v>
@@ -14467,7 +14452,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>7</v>
@@ -14498,7 +14483,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>5</v>
@@ -14529,7 +14514,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>7</v>
@@ -14560,7 +14545,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>3</v>
@@ -14591,7 +14576,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>1</v>

--- a/PROCESSED FILES/TOA - CORRECT ANSWERS.xlsx
+++ b/PROCESSED FILES/TOA - CORRECT ANSWERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivans\Desktop\Archi Reviewer\PROCESSED FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519C7F5D-C024-4B45-A429-63E279126710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3FBDF0-CAF9-4D72-9A26-297536612749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,33 +823,6 @@
   </si>
   <si>
     <t>Social Contact and interaction in a pavillion would be promoted most by which of the following design decision? [A] Making the dimensions of the pavillion small enough so the anticipated number of users would cross into each other's personal distances. [B] Design branches around the support columns so people would have a place to sit and talk [C] organizing the cooking and servicing area distinct from the dining area and entrance [D] Providing an informal variety of spaces of different sizes, locations and uses.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve">A phenomenon of light and visual perception that may be described in terms of an individual's perception of </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>hue, saturation, and lightness</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve"> for objects, and hue, saturation and brightness for light sources (D.K. Ching p. 38) [A] Color [B] Form [C] Texture [D] Shape</t>
-    </r>
   </si>
   <si>
     <t>The distribution of energy emitted by a radiant source, arranged in order of wavelengths especially the band of colors produced when sunlight is refracted and dispersed by a prism, compromising red, orange, yellow, green, blue, indigo and violet (D.K. Ching p. 38) [A] Color [B] Spectrum [C] Hue [D] Saturation</t>
@@ -1463,6 +1436,28 @@
         <rFont val="Century Gothic"/>
       </rPr>
       <t xml:space="preserve"> (D.K. Ching p. 135 (D.K. Ching p. 135) [A] Post Modernism [B] International Style [C] Modernism [D] Abstract Expressionism</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A phenomenon of light and visual perception that may be described in terms of an individual's perception of </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>hue, saturation, and lightness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t xml:space="preserve"> for objects, and hue, saturation and brightness for light sources (D.K. Ching p. 38) [A] Color [B] Form [C] Texture [D] Shape</t>
     </r>
   </si>
 </sst>
@@ -2641,7 +2636,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -5369,7 +5364,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>7</v>
@@ -5524,7 +5519,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>7</v>
@@ -5586,7 +5581,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>7</v>
@@ -10081,7 +10076,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>266</v>
+        <v>416</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>5</v>
@@ -10112,7 +10107,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>7</v>
@@ -10143,7 +10138,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>3</v>
@@ -10174,7 +10169,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>5</v>
@@ -10205,7 +10200,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>1</v>
@@ -10236,7 +10231,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>7</v>
@@ -10267,7 +10262,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>1</v>
@@ -10298,7 +10293,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>3</v>
@@ -10329,7 +10324,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>7</v>
@@ -10360,7 +10355,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>1</v>
@@ -10391,7 +10386,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>5</v>
@@ -10422,7 +10417,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>7</v>
@@ -10453,7 +10448,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>5</v>
@@ -10484,7 +10479,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>7</v>
@@ -10515,7 +10510,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>1</v>
@@ -10546,7 +10541,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>7</v>
@@ -10577,7 +10572,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>3</v>
@@ -10608,7 +10603,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>5</v>
@@ -10639,7 +10634,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>1</v>
@@ -10670,7 +10665,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>5</v>
@@ -10701,7 +10696,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>1</v>
@@ -10732,7 +10727,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>7</v>
@@ -10763,7 +10758,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>3</v>
@@ -10794,7 +10789,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>1</v>
@@ -10825,7 +10820,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>5</v>
@@ -10856,7 +10851,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>7</v>
@@ -10887,7 +10882,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>1</v>
@@ -10918,7 +10913,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>3</v>
@@ -10949,7 +10944,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>5</v>
@@ -10980,7 +10975,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>7</v>
@@ -11011,7 +11006,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>5</v>
@@ -11042,7 +11037,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>7</v>
@@ -11073,7 +11068,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>3</v>
@@ -11104,7 +11099,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>1</v>
@@ -11135,7 +11130,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>7</v>
@@ -11166,7 +11161,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>5</v>
@@ -11197,7 +11192,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>1</v>
@@ -11228,7 +11223,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>7</v>
@@ -11259,7 +11254,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>5</v>
@@ -11290,7 +11285,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>1</v>
@@ -11321,7 +11316,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>7</v>
@@ -11352,7 +11347,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>5</v>
@@ -11383,7 +11378,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>5</v>
@@ -11414,7 +11409,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>5</v>
@@ -11445,7 +11440,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>7</v>
@@ -11476,7 +11471,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>1</v>
@@ -11507,7 +11502,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>7</v>
@@ -11538,7 +11533,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>7</v>
@@ -11569,7 +11564,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>5</v>
@@ -11600,7 +11595,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>5</v>
@@ -11631,7 +11626,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>7</v>
@@ -11662,7 +11657,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>5</v>
@@ -11693,7 +11688,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>1</v>
@@ -11724,7 +11719,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>7</v>
@@ -11755,7 +11750,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>5</v>
@@ -11786,7 +11781,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>1</v>
@@ -11817,7 +11812,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>1</v>
@@ -11848,7 +11843,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>1</v>
@@ -11879,7 +11874,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>5</v>
@@ -11910,7 +11905,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>7</v>
@@ -11941,7 +11936,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>7</v>
@@ -11972,7 +11967,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>3</v>
@@ -12003,7 +11998,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>5</v>
@@ -12034,7 +12029,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>3</v>
@@ -12065,7 +12060,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>1</v>
@@ -12096,7 +12091,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>7</v>
@@ -12127,7 +12122,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>1</v>
@@ -12158,7 +12153,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>7</v>
@@ -12189,7 +12184,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>5</v>
@@ -12220,7 +12215,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>1</v>
@@ -12251,7 +12246,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>5</v>
@@ -12282,7 +12277,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>5</v>
@@ -12313,7 +12308,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>5</v>
@@ -12344,7 +12339,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>1</v>
@@ -12375,7 +12370,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>7</v>
@@ -12406,7 +12401,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>1</v>
@@ -12437,7 +12432,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>1</v>
@@ -12468,7 +12463,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>7</v>
@@ -12499,7 +12494,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>1</v>
@@ -12530,7 +12525,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>7</v>
@@ -12561,7 +12556,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>1</v>
@@ -12592,7 +12587,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>7</v>
@@ -12623,7 +12618,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>5</v>
@@ -12654,7 +12649,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>1</v>
@@ -12685,7 +12680,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>7</v>
@@ -12716,7 +12711,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>3</v>
@@ -12747,7 +12742,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>7</v>
@@ -12778,10 +12773,10 @@
         <v>354</v>
       </c>
       <c r="B354" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C354" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="C354" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="D354" s="3"/>
       <c r="E354" s="3"/>
@@ -12809,10 +12804,10 @@
         <v>355</v>
       </c>
       <c r="B355" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="D355" s="3"/>
       <c r="E355" s="3"/>
@@ -12840,7 +12835,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>5</v>
@@ -12871,7 +12866,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>7</v>
@@ -12902,7 +12897,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>1</v>
@@ -12933,7 +12928,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>3</v>
@@ -12964,7 +12959,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>1</v>
@@ -12995,7 +12990,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>1</v>
@@ -13026,7 +13021,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>1</v>
@@ -13057,7 +13052,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>1</v>
@@ -13088,7 +13083,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>7</v>
@@ -13119,7 +13114,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C365" s="11" t="s">
         <v>3</v>
@@ -13150,7 +13145,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>1</v>
@@ -13181,7 +13176,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>7</v>
@@ -13212,7 +13207,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>1</v>
@@ -13243,7 +13238,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>5</v>
@@ -13274,7 +13269,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>7</v>
@@ -13305,7 +13300,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>5</v>
@@ -13336,7 +13331,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>7</v>
@@ -13367,7 +13362,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>5</v>
@@ -13398,7 +13393,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>3</v>
@@ -13429,7 +13424,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>7</v>
@@ -13460,7 +13455,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>5</v>
@@ -13491,7 +13486,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>5</v>
@@ -13522,7 +13517,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>1</v>
@@ -13553,7 +13548,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>5</v>
@@ -13584,7 +13579,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>1</v>
@@ -13615,7 +13610,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C381" s="12" t="s">
         <v>5</v>
@@ -13646,7 +13641,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>3</v>
@@ -13677,7 +13672,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>1</v>
@@ -13708,7 +13703,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>7</v>
@@ -13739,7 +13734,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>5</v>
@@ -13770,7 +13765,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>3</v>
@@ -13801,7 +13796,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>3</v>
@@ -13832,7 +13827,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>1</v>
@@ -13863,7 +13858,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>7</v>
@@ -13894,7 +13889,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>5</v>
@@ -13925,7 +13920,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>1</v>
@@ -13956,7 +13951,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>7</v>
@@ -13987,7 +13982,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>1</v>
@@ -14018,7 +14013,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>7</v>
@@ -14049,7 +14044,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>1</v>
@@ -14080,7 +14075,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>1</v>
@@ -14111,7 +14106,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>1</v>
@@ -14142,7 +14137,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>7</v>
@@ -14173,7 +14168,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>5</v>
@@ -14204,7 +14199,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>3</v>
@@ -14235,7 +14230,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>7</v>
@@ -14297,7 +14292,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>1</v>
@@ -14328,7 +14323,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>1</v>
@@ -14359,7 +14354,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>1</v>
@@ -14390,7 +14385,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>1</v>
@@ -14421,7 +14416,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>1</v>
@@ -14452,7 +14447,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>7</v>
@@ -14483,7 +14478,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>5</v>
@@ -14514,7 +14509,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>7</v>
@@ -14545,7 +14540,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>3</v>
@@ -14576,7 +14571,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>1</v>

--- a/PROCESSED FILES/TOA - CORRECT ANSWERS.xlsx
+++ b/PROCESSED FILES/TOA - CORRECT ANSWERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivans\Desktop\Archi Reviewer\PROCESSED FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3FBDF0-CAF9-4D72-9A26-297536612749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34FB293-9701-4422-A7AA-D921741B519E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -942,60 +942,6 @@
     <t>Stress or prominence given to an element of a composition by means of contrast, anomaly and counterpoint (D.K. Ching p. 53) [A] Unity [B] Balance [C] Emphasis [D] Harmony</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve">The pleasing or harmonious arrangement or </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>proportion</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve"> of parts or elements in a design composition (D.K. Ching p. 54) [A] Unity [B] Balance [C] Emphasis [D] Harmony</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve">Movement characterized by a patterned </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>repitition or alternation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve"> of formal elements or motifs in the same or modified form (D.K. Ching p. 55) [A] Rhythm [B] Unity [C] Harmony [D] Equilibrium</t>
-    </r>
-  </si>
-  <si>
     <t>The comparative, proper, harmonious relation of one part to another or to the whole with respect to magnitude, quantity or degree (D.K. Ching p. 56) [A] Proportion [B] Scale [C] Equilibrium [D] Balance</t>
   </si>
   <si>
@@ -1005,33 +951,6 @@
     <t>A certain proportionate size, extent or degree. Usually judge in relation to some standard point of reference (D.K. Ching p. 56) [A] Proportion [B] Scale [C] Equilibrium [D] Balance</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve">An applied science concerned with the characteristics of people that need to be considered in the design of devices and systems in order that </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>people and things will interact effectivly and safely</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>. Also called as human engineering (D.K. Ching p. 57) [A] Anthropometrics [B] Proxemics [C] Ergonomics [D] Economics</t>
-    </r>
-  </si>
-  <si>
     <t>The size or proportion of something relative to an accepted standard of measurement (D.K. Ching p. 56) [A] Human Scale [B] Mechanical Scale [C] Visual Scale [D] Generic Scale</t>
   </si>
   <si>
@@ -1090,33 +1009,6 @@
   </si>
   <si>
     <t>An underlying organizationan pattern or structure for a design (D.K. Ching p. 59) [A] Idea [B] Scheme [C] Design Concept [D] Analogy</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>concept for the form</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Century Gothic"/>
-      </rPr>
-      <t>, structure and featues of a building or other construction, represented graphically by diagrams, plans and other drawings (D.K. Ching p. 59) [A] Idea [B] Scheme [C] Design Concept [D] Analogy</t>
-    </r>
   </si>
   <si>
     <t>The faculty of seeing things in her true relations or of evaluating their relative significance (D.K. Ching p. 59) [A] Vision [B] Perspective [C] View [D] Aspect</t>
@@ -1458,6 +1350,94 @@
         <rFont val="Century Gothic"/>
       </rPr>
       <t xml:space="preserve"> for objects, and hue, saturation and brightness for light sources (D.K. Ching p. 38) [A] Color [B] Form [C] Texture [D] Shape</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The pleasing or harmonious arrangement or </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>proportion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t xml:space="preserve"> of parts or elements in a design composition (D.K. Ching p. 54) [A] Unity [B] Balance [C] Emphasis [D] Harmony</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Movement characterized by a patterned </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>repitition or alternation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t xml:space="preserve"> of formal elements or motifs in the same or modified form (D.K. Ching p. 55) [A] Rhythm [B] Unity [C] Harmony [D] Equilibrium</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">An applied science concerned with the characteristics of people that need to be considered in the design of devices and systems in order that </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>people and things will interact effectivly and safely</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>. Also called as human engineering (D.K. Ching p. 57) [A] Anthropometrics [B] Proxemics [C] Ergonomics [D] Economics</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>concept for the form</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Century Gothic"/>
+      </rPr>
+      <t>, structure and featues of a building or other construction, represented graphically by diagrams, plans and other drawings (D.K. Ching p. 59) [A] Idea [B] Scheme [C] Design Concept [D] Analogy</t>
     </r>
   </si>
 </sst>
@@ -2636,7 +2616,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -5364,7 +5344,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>7</v>
@@ -5519,7 +5499,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>7</v>
@@ -5581,7 +5561,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>7</v>
@@ -10076,7 +10056,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>5</v>
@@ -11316,7 +11296,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>305</v>
+        <v>413</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>7</v>
@@ -11347,7 +11327,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>306</v>
+        <v>414</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>5</v>
@@ -11378,7 +11358,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>5</v>
@@ -11409,7 +11389,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>5</v>
@@ -11440,7 +11420,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>7</v>
@@ -11471,7 +11451,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>310</v>
+        <v>415</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>1</v>
@@ -11502,7 +11482,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>7</v>
@@ -11533,7 +11513,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>7</v>
@@ -11564,7 +11544,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>5</v>
@@ -11595,7 +11575,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>5</v>
@@ -11626,7 +11606,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>7</v>
@@ -11657,7 +11637,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>5</v>
@@ -11688,7 +11668,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>1</v>
@@ -11719,7 +11699,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>7</v>
@@ -11750,7 +11730,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>5</v>
@@ -11781,7 +11761,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>1</v>
@@ -11812,7 +11792,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>1</v>
@@ -11843,7 +11823,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>1</v>
@@ -11874,7 +11854,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>5</v>
@@ -11905,7 +11885,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>7</v>
@@ -11936,7 +11916,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>7</v>
@@ -11967,7 +11947,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>3</v>
@@ -11998,7 +11978,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>5</v>
@@ -12029,7 +12009,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>3</v>
@@ -12060,7 +12040,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>1</v>
@@ -12091,7 +12071,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>7</v>
@@ -12122,7 +12102,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>331</v>
+        <v>416</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>1</v>
@@ -12153,7 +12133,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>7</v>
@@ -12184,7 +12164,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>5</v>
@@ -12215,7 +12195,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>1</v>
@@ -12246,7 +12226,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>5</v>
@@ -12277,7 +12257,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>5</v>
@@ -12308,7 +12288,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>5</v>
@@ -12339,7 +12319,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>1</v>
@@ -12370,7 +12350,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>7</v>
@@ -12401,7 +12381,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>1</v>
@@ -12432,7 +12412,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>1</v>
@@ -12463,7 +12443,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>7</v>
@@ -12494,7 +12474,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>1</v>
@@ -12525,7 +12505,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>7</v>
@@ -12556,7 +12536,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>1</v>
@@ -12587,7 +12567,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>7</v>
@@ -12618,7 +12598,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>5</v>
@@ -12649,7 +12629,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>1</v>
@@ -12680,7 +12660,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>7</v>
@@ -12711,7 +12691,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>3</v>
@@ -12742,7 +12722,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>7</v>
@@ -12773,10 +12753,10 @@
         <v>354</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D354" s="3"/>
       <c r="E354" s="3"/>
@@ -12804,10 +12784,10 @@
         <v>355</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D355" s="3"/>
       <c r="E355" s="3"/>
@@ -12835,7 +12815,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>5</v>
@@ -12866,7 +12846,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>7</v>
@@ -12897,7 +12877,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>1</v>
@@ -12928,7 +12908,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>3</v>
@@ -12959,7 +12939,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>1</v>
@@ -12990,7 +12970,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>1</v>
@@ -13021,7 +13001,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>1</v>
@@ -13052,7 +13032,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>1</v>
@@ -13083,7 +13063,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>7</v>
@@ -13114,7 +13094,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C365" s="11" t="s">
         <v>3</v>
@@ -13145,7 +13125,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>1</v>
@@ -13176,7 +13156,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>7</v>
@@ -13207,7 +13187,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>1</v>
@@ -13238,7 +13218,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>5</v>
@@ -13269,7 +13249,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>7</v>
@@ -13300,7 +13280,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>5</v>
@@ -13331,7 +13311,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>7</v>
@@ -13362,7 +13342,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>5</v>
@@ -13393,7 +13373,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>3</v>
@@ -13424,7 +13404,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>7</v>
@@ -13455,7 +13435,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>5</v>
@@ -13486,7 +13466,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>5</v>
@@ -13517,7 +13497,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>1</v>
@@ -13548,7 +13528,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>5</v>
@@ -13579,7 +13559,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>1</v>
@@ -13610,7 +13590,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="12" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C381" s="12" t="s">
         <v>5</v>
@@ -13641,7 +13621,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>3</v>
@@ -13672,7 +13652,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>1</v>
@@ -13703,7 +13683,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>7</v>
@@ -13734,7 +13714,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>5</v>
@@ -13765,7 +13745,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>3</v>
@@ -13796,7 +13776,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>3</v>
@@ -13827,7 +13807,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>1</v>
@@ -13858,7 +13838,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>7</v>
@@ -13889,7 +13869,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>5</v>
@@ -13920,7 +13900,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>1</v>
@@ -13951,7 +13931,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>7</v>
@@ -13982,7 +13962,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>1</v>
@@ -14013,7 +13993,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>7</v>
@@ -14044,7 +14024,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>1</v>
@@ -14075,7 +14055,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>1</v>
@@ -14106,7 +14086,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>1</v>
@@ -14137,7 +14117,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>7</v>
@@ -14168,7 +14148,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>5</v>
@@ -14199,7 +14179,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>3</v>
@@ -14230,7 +14210,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>7</v>
@@ -14292,7 +14272,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>1</v>
@@ -14323,7 +14303,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C404" s="2" t="s">
         <v>1</v>
@@ -14354,7 +14334,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C405" s="2" t="s">
         <v>1</v>
@@ -14385,7 +14365,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>1</v>
@@ -14416,7 +14396,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>1</v>
@@ -14447,7 +14427,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>7</v>
@@ -14478,7 +14458,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C409" s="2" t="s">
         <v>5</v>
@@ -14509,7 +14489,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C410" s="2" t="s">
         <v>7</v>
@@ -14540,7 +14520,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C411" s="2" t="s">
         <v>3</v>
@@ -14571,7 +14551,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C412" s="2" t="s">
         <v>1</v>
